--- a/excel/edge_key.xlsx
+++ b/excel/edge_key.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mosby\Desktop\学习文件\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\Ai\小程序\Excel显示\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D57F0B-0227-432C-ACF6-22EFA25B65F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD029644-DD9C-4137-BF5A-4571C5FB349A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{FE1719C2-E13F-4248-9A1E-AF19344DE301}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="339">
   <si>
     <t>Show or hide the favorites bar</t>
   </si>
@@ -1051,6 +1051,9 @@
   </si>
   <si>
     <t>转至上一选项卡</t>
+  </si>
+  <si>
+    <t>说明2</t>
   </si>
 </sst>
 </file>
@@ -1115,6 +1118,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5C485D6E-FAB3-4BEA-9E13-3D1CFC9B2406}" name="表2" displayName="表2" ref="A1:C85" totalsRowShown="0">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{F6264314-C923-4906-A7B2-44D798D480D4}" name="快捷键"/>
+    <tableColumn id="2" xr3:uid="{8172CF53-079E-44A9-85CF-FD0D08CDD9B3}" name="说明"/>
+    <tableColumn id="3" xr3:uid="{3684CD37-7F0A-4D3B-98CF-438D166DB043}" name="说明2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B3EDC94B-6989-4456-B880-1A9AB725DF3F}" name="表3" displayName="表3" ref="A1:C61" totalsRowShown="0">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{E76EC04D-A301-4EA4-9A2F-BF2C675430DD}" name="快捷键"/>
+    <tableColumn id="2" xr3:uid="{57B7E66B-1065-4CD8-951B-8CC0BF1FAF2E}" name="说明"/>
+    <tableColumn id="3" xr3:uid="{5DB5F5C2-3A98-4017-A986-5AA29EEE9537}" name="说明2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1417,12 +1442,12 @@
   <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.86328125" customWidth="1"/>
+    <col min="1" max="1" width="22.73046875" customWidth="1"/>
     <col min="2" max="2" width="59.19921875" customWidth="1"/>
     <col min="3" max="3" width="76" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -1430,10 +1455,10 @@
         <v>231</v>
       </c>
       <c r="C1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>90</v>
       </c>
@@ -1444,7 +1469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -1455,7 +1480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -1466,7 +1491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -1477,7 +1502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -1488,7 +1513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>95</v>
       </c>
@@ -1499,7 +1524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>96</v>
       </c>
@@ -1510,7 +1535,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>97</v>
       </c>
@@ -1521,7 +1546,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -1532,7 +1557,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>100</v>
       </c>
@@ -1543,7 +1568,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>101</v>
       </c>
@@ -1554,7 +1579,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>102</v>
       </c>
@@ -1565,7 +1590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>103</v>
       </c>
@@ -1576,7 +1601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>104</v>
       </c>
@@ -1587,7 +1612,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>105</v>
       </c>
@@ -1598,7 +1623,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>106</v>
       </c>
@@ -1609,7 +1634,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>107</v>
       </c>
@@ -1620,7 +1645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>108</v>
       </c>
@@ -1631,7 +1656,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>109</v>
       </c>
@@ -1642,7 +1667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -1653,7 +1678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>111</v>
       </c>
@@ -1664,7 +1689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>112</v>
       </c>
@@ -1675,7 +1700,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -1686,7 +1711,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -1697,7 +1722,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>114</v>
       </c>
@@ -1708,7 +1733,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>115</v>
       </c>
@@ -1719,7 +1744,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>116</v>
       </c>
@@ -1730,7 +1755,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>117</v>
       </c>
@@ -1741,7 +1766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1752,7 +1777,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>118</v>
       </c>
@@ -1763,7 +1788,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>119</v>
       </c>
@@ -1774,7 +1799,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>120</v>
       </c>
@@ -1785,7 +1810,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>121</v>
       </c>
@@ -1796,7 +1821,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>122</v>
       </c>
@@ -1807,7 +1832,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>123</v>
       </c>
@@ -1818,7 +1843,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>124</v>
       </c>
@@ -1829,7 +1854,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>125</v>
       </c>
@@ -1840,7 +1865,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>126</v>
       </c>
@@ -1851,7 +1876,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>127</v>
       </c>
@@ -1862,7 +1887,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>128</v>
       </c>
@@ -1873,7 +1898,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>129</v>
       </c>
@@ -1884,7 +1909,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>130</v>
       </c>
@@ -1895,7 +1920,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>131</v>
       </c>
@@ -1906,7 +1931,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>132</v>
       </c>
@@ -1917,7 +1942,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>133</v>
       </c>
@@ -1928,7 +1953,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>134</v>
       </c>
@@ -1939,7 +1964,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>135</v>
       </c>
@@ -1950,7 +1975,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>136</v>
       </c>
@@ -1961,7 +1986,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>137</v>
       </c>
@@ -1972,7 +1997,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>138</v>
       </c>
@@ -1983,7 +2008,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>139</v>
       </c>
@@ -1994,7 +2019,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>140</v>
       </c>
@@ -2005,7 +2030,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>50</v>
       </c>
@@ -2016,7 +2041,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>142</v>
       </c>
@@ -2027,7 +2052,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>143</v>
       </c>
@@ -2038,7 +2063,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>144</v>
       </c>
@@ -2049,7 +2074,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>145</v>
       </c>
@@ -2060,7 +2085,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>54</v>
       </c>
@@ -2071,7 +2096,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>56</v>
       </c>
@@ -2082,7 +2107,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>58</v>
       </c>
@@ -2093,7 +2118,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>146</v>
       </c>
@@ -2104,7 +2129,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>60</v>
       </c>
@@ -2115,7 +2140,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>147</v>
       </c>
@@ -2126,7 +2151,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -2137,7 +2162,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>148</v>
       </c>
@@ -2148,7 +2173,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>149</v>
       </c>
@@ -2159,7 +2184,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -2170,7 +2195,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>69</v>
       </c>
@@ -2181,7 +2206,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -2192,7 +2217,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>150</v>
       </c>
@@ -2203,7 +2228,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>152</v>
       </c>
@@ -2214,7 +2239,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -2225,7 +2250,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -2236,7 +2261,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -2247,7 +2272,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -2258,7 +2283,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -2269,7 +2294,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -2280,7 +2305,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>154</v>
       </c>
@@ -2291,7 +2316,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -2302,7 +2327,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>155</v>
       </c>
@@ -2313,7 +2338,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2324,7 +2349,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -2335,7 +2360,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -2346,7 +2371,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>156</v>
       </c>
@@ -2360,6 +2385,9 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -2368,12 +2396,12 @@
   <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="42.73046875" customWidth="1"/>
+    <col min="1" max="1" width="33.9296875" customWidth="1"/>
+    <col min="2" max="2" width="51.796875" customWidth="1"/>
     <col min="3" max="3" width="50.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -2381,10 +2409,10 @@
         <v>231</v>
       </c>
       <c r="C1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>232</v>
       </c>
@@ -2395,7 +2423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>233</v>
       </c>
@@ -2406,7 +2434,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>235</v>
       </c>
@@ -2417,7 +2445,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>237</v>
       </c>
@@ -2428,7 +2456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>238</v>
       </c>
@@ -2439,7 +2467,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>239</v>
       </c>
@@ -2450,7 +2478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>240</v>
       </c>
@@ -2461,7 +2489,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>242</v>
       </c>
@@ -2472,7 +2500,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>244</v>
       </c>
@@ -2483,7 +2511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>245</v>
       </c>
@@ -2494,7 +2522,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>246</v>
       </c>
@@ -2505,7 +2533,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>247</v>
       </c>
@@ -2516,7 +2544,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>249</v>
       </c>
@@ -2527,7 +2555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>250</v>
       </c>
@@ -2538,7 +2566,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>111</v>
       </c>
@@ -2549,7 +2577,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>252</v>
       </c>
@@ -2560,7 +2588,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>254</v>
       </c>
@@ -2571,7 +2599,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>256</v>
       </c>
@@ -2582,7 +2610,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>258</v>
       </c>
@@ -2593,7 +2621,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>259</v>
       </c>
@@ -2604,7 +2632,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>261</v>
       </c>
@@ -2615,7 +2643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>262</v>
       </c>
@@ -2626,7 +2654,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>264</v>
       </c>
@@ -2637,7 +2665,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>266</v>
       </c>
@@ -2648,7 +2676,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>267</v>
       </c>
@@ -2659,7 +2687,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>268</v>
       </c>
@@ -2670,7 +2698,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>270</v>
       </c>
@@ -2681,7 +2709,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>272</v>
       </c>
@@ -2692,7 +2720,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>273</v>
       </c>
@@ -2703,7 +2731,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>274</v>
       </c>
@@ -2714,7 +2742,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>276</v>
       </c>
@@ -2725,7 +2753,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>277</v>
       </c>
@@ -2736,7 +2764,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>278</v>
       </c>
@@ -2747,7 +2775,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>279</v>
       </c>
@@ -2758,7 +2786,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>281</v>
       </c>
@@ -2769,7 +2797,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>282</v>
       </c>
@@ -2780,7 +2808,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>283</v>
       </c>
@@ -2791,7 +2819,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>285</v>
       </c>
@@ -2802,7 +2830,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>287</v>
       </c>
@@ -2813,7 +2841,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>289</v>
       </c>
@@ -2824,7 +2852,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>291</v>
       </c>
@@ -2835,7 +2863,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>292</v>
       </c>
@@ -2846,7 +2874,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>293</v>
       </c>
@@ -2857,7 +2885,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>294</v>
       </c>
@@ -2868,7 +2896,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>295</v>
       </c>
@@ -2879,7 +2907,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>296</v>
       </c>
@@ -2890,7 +2918,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>297</v>
       </c>
@@ -2901,7 +2929,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>299</v>
       </c>
@@ -2912,7 +2940,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>301</v>
       </c>
@@ -2923,7 +2951,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>302</v>
       </c>
@@ -2934,7 +2962,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -2945,7 +2973,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>75</v>
       </c>
@@ -2956,7 +2984,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>304</v>
       </c>
@@ -2967,7 +2995,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>306</v>
       </c>
@@ -2978,7 +3006,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>307</v>
       </c>
@@ -2989,7 +3017,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>153</v>
       </c>
@@ -3000,7 +3028,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>87</v>
       </c>
@@ -3011,7 +3039,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>156</v>
       </c>
@@ -3022,7 +3050,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>310</v>
       </c>
@@ -3033,7 +3061,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>312</v>
       </c>
@@ -3047,5 +3075,8 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/excel/edge_key.xlsx
+++ b/excel/edge_key.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\Ai\小程序\Excel显示\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD029644-DD9C-4137-BF5A-4571C5FB349A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63CA2A5-4DB8-4E00-8273-DEED32821C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{FE1719C2-E13F-4248-9A1E-AF19344DE301}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{FE1719C2-E13F-4248-9A1E-AF19344DE301}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
     <sheet name="Mac" sheetId="2" r:id="rId2"/>
+    <sheet name="Mac测试" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="340">
   <si>
     <t>Show or hide the favorites bar</t>
   </si>
@@ -1054,6 +1055,10 @@
   </si>
   <si>
     <t>说明2</t>
+  </si>
+  <si>
+    <t>说明2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1139,6 +1144,18 @@
     <tableColumn id="3" xr3:uid="{5DB5F5C2-3A98-4017-A986-5AA29EEE9537}" name="说明2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C629A734-BFC3-4317-A77C-3F74E977D0D4}" name="表1" displayName="表1" ref="A1:C60" totalsRowShown="0">
+  <autoFilter ref="A1:C60" xr:uid="{C629A734-BFC3-4317-A77C-3F74E977D0D4}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{F3E137CB-4994-42ED-A38E-21B7E706765F}" name="Command+Shift+B"/>
+    <tableColumn id="2" xr3:uid="{62BC9604-33B7-4590-84B3-FF4B067DB55A}" name="显示或隐藏收藏夹栏"/>
+    <tableColumn id="3" xr3:uid="{45BF6CF9-A825-4E4A-821C-2987C036ADEC}" name="Show or hide the favorites bar"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1442,9 +1459,9 @@
   <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="22.73046875" customWidth="1"/>
-    <col min="2" max="2" width="59.19921875" customWidth="1"/>
-    <col min="3" max="3" width="76" customWidth="1"/>
+    <col min="1" max="1" width="26.59765625" customWidth="1"/>
+    <col min="2" max="2" width="60.59765625" customWidth="1"/>
+    <col min="3" max="3" width="80.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -1455,7 +1472,7 @@
         <v>231</v>
       </c>
       <c r="C1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -2396,9 +2413,9 @@
   <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="33.9296875" customWidth="1"/>
-    <col min="2" max="2" width="51.796875" customWidth="1"/>
-    <col min="3" max="3" width="50.73046875" customWidth="1"/>
+    <col min="1" max="1" width="26.59765625" customWidth="1"/>
+    <col min="2" max="2" width="60.59765625" customWidth="1"/>
+    <col min="3" max="3" width="80.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -3069,6 +3086,685 @@
         <v>337</v>
       </c>
       <c r="C61" t="s">
+        <v>313</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E2D715-83A6-4B3B-A1AC-48A0F81BDCEE}">
+  <dimension ref="A1:C60"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="31.3984375" customWidth="1"/>
+    <col min="2" max="2" width="60.73046875" customWidth="1"/>
+    <col min="3" max="3" width="56.1328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B8" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>245</v>
+      </c>
+      <c r="B10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C12" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C16" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>254</v>
+      </c>
+      <c r="B17" t="s">
+        <v>319</v>
+      </c>
+      <c r="C17" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>258</v>
+      </c>
+      <c r="B19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>259</v>
+      </c>
+      <c r="B20" t="s">
+        <v>320</v>
+      </c>
+      <c r="C20" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>261</v>
+      </c>
+      <c r="B21" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>262</v>
+      </c>
+      <c r="B22" t="s">
+        <v>321</v>
+      </c>
+      <c r="C22" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" t="s">
+        <v>265</v>
+      </c>
+      <c r="C23" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>266</v>
+      </c>
+      <c r="B24" t="s">
+        <v>213</v>
+      </c>
+      <c r="C24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>267</v>
+      </c>
+      <c r="B25" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>268</v>
+      </c>
+      <c r="B26" t="s">
+        <v>322</v>
+      </c>
+      <c r="C26" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>270</v>
+      </c>
+      <c r="B27" t="s">
+        <v>323</v>
+      </c>
+      <c r="C27" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>272</v>
+      </c>
+      <c r="B28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>273</v>
+      </c>
+      <c r="B29" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>274</v>
+      </c>
+      <c r="B30" t="s">
+        <v>324</v>
+      </c>
+      <c r="C30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>277</v>
+      </c>
+      <c r="B32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>278</v>
+      </c>
+      <c r="B33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>279</v>
+      </c>
+      <c r="B34" t="s">
+        <v>325</v>
+      </c>
+      <c r="C34" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>281</v>
+      </c>
+      <c r="B35" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>282</v>
+      </c>
+      <c r="B36" t="s">
+        <v>196</v>
+      </c>
+      <c r="C36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>283</v>
+      </c>
+      <c r="B37" t="s">
+        <v>326</v>
+      </c>
+      <c r="C37" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>285</v>
+      </c>
+      <c r="B38" t="s">
+        <v>327</v>
+      </c>
+      <c r="C38" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>287</v>
+      </c>
+      <c r="B39" t="s">
+        <v>328</v>
+      </c>
+      <c r="C39" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>289</v>
+      </c>
+      <c r="B40" t="s">
+        <v>329</v>
+      </c>
+      <c r="C40" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>291</v>
+      </c>
+      <c r="B41" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>292</v>
+      </c>
+      <c r="B42" t="s">
+        <v>200</v>
+      </c>
+      <c r="C42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>293</v>
+      </c>
+      <c r="B43" t="s">
+        <v>201</v>
+      </c>
+      <c r="C43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>294</v>
+      </c>
+      <c r="B44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C44" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>295</v>
+      </c>
+      <c r="B45" t="s">
+        <v>203</v>
+      </c>
+      <c r="C45" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>296</v>
+      </c>
+      <c r="B46" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>297</v>
+      </c>
+      <c r="B47" t="s">
+        <v>330</v>
+      </c>
+      <c r="C47" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>299</v>
+      </c>
+      <c r="B48" t="s">
+        <v>331</v>
+      </c>
+      <c r="C48" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>301</v>
+      </c>
+      <c r="B49" t="s">
+        <v>198</v>
+      </c>
+      <c r="C49" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>302</v>
+      </c>
+      <c r="B50" t="s">
+        <v>199</v>
+      </c>
+      <c r="C50" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" t="s">
+        <v>219</v>
+      </c>
+      <c r="C51" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>304</v>
+      </c>
+      <c r="B53" t="s">
+        <v>333</v>
+      </c>
+      <c r="C53" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>306</v>
+      </c>
+      <c r="B54" t="s">
+        <v>223</v>
+      </c>
+      <c r="C54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>307</v>
+      </c>
+      <c r="B55" t="s">
+        <v>224</v>
+      </c>
+      <c r="C55" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>153</v>
+      </c>
+      <c r="B56" t="s">
+        <v>225</v>
+      </c>
+      <c r="C56" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>87</v>
+      </c>
+      <c r="B57" t="s">
+        <v>334</v>
+      </c>
+      <c r="C57" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>156</v>
+      </c>
+      <c r="B58" t="s">
+        <v>335</v>
+      </c>
+      <c r="C58" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>310</v>
+      </c>
+      <c r="B59" t="s">
+        <v>336</v>
+      </c>
+      <c r="C59" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>312</v>
+      </c>
+      <c r="B60" t="s">
+        <v>337</v>
+      </c>
+      <c r="C60" t="s">
         <v>313</v>
       </c>
     </row>

--- a/excel/edge_key.xlsx
+++ b/excel/edge_key.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\Ai\小程序\Excel显示\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63CA2A5-4DB8-4E00-8273-DEED32821C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4500A1C-C447-4A68-BA33-9D1740E6DF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{FE1719C2-E13F-4248-9A1E-AF19344DE301}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="4" xr2:uid="{FE1719C2-E13F-4248-9A1E-AF19344DE301}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
     <sheet name="Mac" sheetId="2" r:id="rId2"/>
     <sheet name="Mac测试" sheetId="3" r:id="rId3"/>
+    <sheet name="超级表各种样式支持" sheetId="4" r:id="rId4"/>
+    <sheet name="超级表各种样式支持 (2)" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="362">
   <si>
     <t>Show or hide the favorites bar</t>
   </si>
@@ -1059,6 +1061,72 @@
   <si>
     <t>说明2</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汇总</t>
+  </si>
+  <si>
+    <t>产品</t>
+  </si>
+  <si>
+    <t>客户</t>
+  </si>
+  <si>
+    <t>第 1 季度</t>
+  </si>
+  <si>
+    <t>第 2 季度</t>
+  </si>
+  <si>
+    <t>第 3 季度</t>
+  </si>
+  <si>
+    <t>Alice Mutton（爱丽丝羊肉）</t>
+  </si>
+  <si>
+    <t>ANTON</t>
+  </si>
+  <si>
+    <t>BERGS</t>
+  </si>
+  <si>
+    <t>BOLID</t>
+  </si>
+  <si>
+    <t>BOTTM</t>
+  </si>
+  <si>
+    <t>ERNSH</t>
+  </si>
+  <si>
+    <t>GODOS</t>
+  </si>
+  <si>
+    <t>HUNGC</t>
+  </si>
+  <si>
+    <t>PICCO</t>
+  </si>
+  <si>
+    <t>RATTC</t>
+  </si>
+  <si>
+    <t>REGGC</t>
+  </si>
+  <si>
+    <t>SAVEA</t>
+  </si>
+  <si>
+    <t>SEVES</t>
+  </si>
+  <si>
+    <t>WHITC</t>
+  </si>
+  <si>
+    <t>Aniseed Syrup（茴香糖浆）</t>
+  </si>
+  <si>
+    <t>ALFKI</t>
   </si>
 </sst>
 </file>
@@ -1082,12 +1150,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1104,8 +1178,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1148,14 +1225,62 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C629A734-BFC3-4317-A77C-3F74E977D0D4}" name="表1" displayName="表1" ref="A1:C60" totalsRowShown="0">
-  <autoFilter ref="A1:C60" xr:uid="{C629A734-BFC3-4317-A77C-3F74E977D0D4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C629A734-BFC3-4317-A77C-3F74E977D0D4}" name="表1" displayName="表1" ref="A1:C60">
+  <autoFilter ref="A1:C60" xr:uid="{C629A734-BFC3-4317-A77C-3F74E977D0D4}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F3E137CB-4994-42ED-A38E-21B7E706765F}" name="Command+Shift+B"/>
+    <tableColumn id="1" xr3:uid="{F3E137CB-4994-42ED-A38E-21B7E706765F}" name="Command+Shift+B" totalsRowLabel="汇总"/>
     <tableColumn id="2" xr3:uid="{62BC9604-33B7-4590-84B3-FF4B067DB55A}" name="显示或隐藏收藏夹栏"/>
-    <tableColumn id="3" xr3:uid="{45BF6CF9-A825-4E4A-821C-2987C036ADEC}" name="Show or hide the favorites bar"/>
+    <tableColumn id="3" xr3:uid="{45BF6CF9-A825-4E4A-821C-2987C036ADEC}" name="Show or hide the favorites bar" totalsRowFunction="count"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleDark6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleDark3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3E0D2885-3418-4B4D-971B-5A03E6154661}" name="表4" displayName="表4" ref="A1:F18" totalsRowCount="1">
+  <autoFilter ref="A1:F17" xr:uid="{3E0D2885-3418-4B4D-971B-5A03E6154661}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{3610186F-35A0-47B7-8386-23160BC50137}" name="产品" totalsRowLabel="汇总"/>
+    <tableColumn id="2" xr3:uid="{FC8E056A-70B1-4D73-9ABE-4C2880CFF14F}" name="客户"/>
+    <tableColumn id="3" xr3:uid="{5A18F56E-24F3-4996-B8F3-8E12BD38EB0A}" name="第 1 季度"/>
+    <tableColumn id="4" xr3:uid="{CEA39F80-EF62-49BB-8499-AEC3AD81931B}" name="第 2 季度"/>
+    <tableColumn id="5" xr3:uid="{CE28D1BA-2C8C-4482-9DD7-EDADB62D185B}" name="第 3 季度"/>
+    <tableColumn id="7" xr3:uid="{F08CD8B3-5257-4124-BE3E-33CBDB756D46}" name="汇总" totalsRowFunction="sum"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0A26DE59-D7A6-427C-9BEA-14F8BE034D15}" name="表4_6" displayName="表4_6" ref="A1:F18" totalsRowCount="1">
+  <autoFilter ref="A1:F17" xr:uid="{3E0D2885-3418-4B4D-971B-5A03E6154661}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{FB7BE3D9-0353-4C7C-81D5-3B2E91CA43B4}" name="产品" totalsRowLabel="汇总"/>
+    <tableColumn id="2" xr3:uid="{58C1226D-39B3-4194-B403-56817F5133FC}" name="客户"/>
+    <tableColumn id="3" xr3:uid="{97652190-3150-491E-9727-7484FCF3A3D6}" name="第 1 季度"/>
+    <tableColumn id="4" xr3:uid="{C8D6A08E-27C3-42B9-99E0-6E8CFCEFD748}" name="第 2 季度"/>
+    <tableColumn id="5" xr3:uid="{EB470F50-1A51-4A00-8916-388D40F0836E}" name="第 3 季度"/>
+    <tableColumn id="7" xr3:uid="{73ED84C3-10E6-4DBC-9448-8A48DF48B609}" name="汇总" totalsRowFunction="sum"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark6" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="1"/>
 </table>
 </file>
 
@@ -3775,4 +3900,740 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1DDC7C8-A802-4B85-8193-56C03F27241D}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="27.46484375" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" customWidth="1"/>
+    <col min="3" max="5" width="10.53125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>702</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C3">
+        <v>312</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C5">
+        <v>1170</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C6">
+        <v>1123.2</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>3730.3500000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>280.8</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>280.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>346</v>
+      </c>
+      <c r="B8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8">
+        <v>62.4</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1560</v>
+      </c>
+      <c r="E9">
+        <v>936</v>
+      </c>
+      <c r="F9">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>346</v>
+      </c>
+      <c r="B10" t="s">
+        <v>355</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>592.79999999999995</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>592.79999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>346</v>
+      </c>
+      <c r="B11" t="s">
+        <v>356</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>3900</v>
+      </c>
+      <c r="F12">
+        <v>4689.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>346</v>
+      </c>
+      <c r="B13" t="s">
+        <v>358</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>877.5</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>877.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>346</v>
+      </c>
+      <c r="B14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>360</v>
+      </c>
+      <c r="B15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>360</v>
+      </c>
+      <c r="B16" t="s">
+        <v>350</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>360</v>
+      </c>
+      <c r="B17" t="s">
+        <v>351</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>340</v>
+      </c>
+      <c r="F18">
+        <f>SUBTOTAL(109,表4[汇总])</f>
+        <v>18044.599999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55FC60A9-A0B0-421C-A757-219E7494B168}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="27.46484375" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" customWidth="1"/>
+    <col min="3" max="5" width="10.53125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>702</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C3">
+        <v>312</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C5">
+        <v>1170</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C6">
+        <v>1123.2</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>3730.3500000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>280.8</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>280.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>346</v>
+      </c>
+      <c r="B8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8">
+        <v>62.4</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1560</v>
+      </c>
+      <c r="E9">
+        <v>936</v>
+      </c>
+      <c r="F9">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>346</v>
+      </c>
+      <c r="B10" t="s">
+        <v>355</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>592.79999999999995</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>592.79999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>346</v>
+      </c>
+      <c r="B11" t="s">
+        <v>356</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>3900</v>
+      </c>
+      <c r="F12">
+        <v>4689.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>346</v>
+      </c>
+      <c r="B13" t="s">
+        <v>358</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>877.5</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>877.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>346</v>
+      </c>
+      <c r="B14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>360</v>
+      </c>
+      <c r="B15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>360</v>
+      </c>
+      <c r="B16" t="s">
+        <v>350</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>360</v>
+      </c>
+      <c r="B17" t="s">
+        <v>351</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>340</v>
+      </c>
+      <c r="F18">
+        <f>SUBTOTAL(109,表4_6[汇总])</f>
+        <v>18044.599999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>